--- a/02_加值成品/八上/八上2-4_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上2-4_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上2-4 水溶液與濃度　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二上學期 八上2-4 水溶液與濃度　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>被溶解的物質稱為？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>溶質</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>溶劑</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>鹽</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>如鹽</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>溶解他物的物質稱為？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>溶液</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>變大</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>溶劑</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>多寡</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>常為水</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>溶液由什麼組成？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>溶質+溶劑</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>鹽</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>溶劑</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>溶液</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>兩者</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>重量百分濃度公式？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>蒸發部分水或加鹽</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>溶液才是總量、比例才正確</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>溶質÷溶液×100%</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>1%=10000ppm</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>含溶質</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>ppm代表什麼？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>鹽</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>百萬分之一</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>溶劑</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>極稀</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>食鹽水中溶質是？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>鹽</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>變大</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>溶劑</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>溶劑是水</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>溶液質量如何算？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>變大</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>百萬分之一</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>溶劑</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>溶質+溶劑</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>總和</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>生理食鹽水濃度約？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>0.9%</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>醫療用</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>溶質溶於溶劑形成？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>溶液</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>百萬分之一</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>溶質+溶劑</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>溶劑</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>溶液</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>濃度表示溶液中溶質的？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>多寡</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>百萬分之一</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>變小</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>濃度</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上2-4 水溶液與濃度　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二上學期 八上2-4 水溶液與濃度　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>20g鹽溶於80g水，濃度？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>20/100</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>10g糖溶於90g水，濃度？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>10/100</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>100g溶液含5g溶質，濃度？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>5/100</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>要配200g的10%鹽水需鹽？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>3.5 g</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>37.5 g</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>20 g</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>5 g</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>200×0.1</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>50g水含0.05g溶質約幾ppm？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>溶液才是總量、比例才正確</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>溶質÷溶液×100%</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>1000 ppm</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>蒸發部分水或加鹽</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>0.05/50×10⁶</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>加水稀釋後溶質質量？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>鹽</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>不變</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>多寡</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>變小</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>只濃度降</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>30g鹽溶於120g水濃度？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>30/150</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>濃度25%的150g溶液含溶質？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>3.5 g</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>5 g</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>20 g</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>37.5 g</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>150×0.25</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>40g鹽溶於160g水濃度？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>40/200</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>配100g的5%糖水需糖？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>37.5 g</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>5 g</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>20 g</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>3.5 g</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>100×0.05</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上2-4 水溶液與濃度　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二上學期 八上2-4 水溶液與濃度　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>為何濃度用溶液而非溶劑當分母？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>1000 ppm</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>溶液才是總量、比例才正確</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>蒸發部分水或加鹽</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1%=10000ppm</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>定義</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>溶質相同、加水後濃度如何變？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>溶質</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>鹽</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>變小</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>溶劑</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>分母變大</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>水中某污染物2mg/1kg水約幾ppm？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>3.5 g</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>37.5 g</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>2 ppm</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>mg/kg</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>40g溶液蒸發掉10g水，剩溶液濃度變？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>百萬分之一</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>溶劑</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>變大</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>多寡</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>溶質不變總量少</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>兩杯同濃度溶液倒一起濃度？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>變大</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>鹽</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>不變</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>溶液</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>同濃度</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>15%的溶液200g與純水混不需算，觀念上濃度？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>變小</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>多寡</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>百萬分之一</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>溶劑</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>稀釋</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>要使10%鹽水變20%可如何？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>溶質÷溶液×100%</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>1%=10000ppm</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>1000 ppm</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>蒸發部分水或加鹽</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>提高溶質比</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>ppm比%小多少倍？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>蒸發部分水或加鹽</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>溶質÷溶液×100%</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>1%=10000ppm</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>溶液才是總量、比例才正確</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>換算</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>100g的10%鹽水加水到200g濃度變？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>稀釋一半</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>海水約3.5%代表100g海水含鹽？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>37.5 g</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>20 g</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>5 g</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>3.5 g</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>百分濃度</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八上/八上2-4_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上2-4_三種難度測驗卷.xlsx
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>50g水含0.05g溶質約幾ppm？</t>
+          <t>50g溶液含0.05g溶質約幾ppm？</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>溶液才是總量、比例才正確</t>
+          <t>蒸發部分水或加鹽</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>蒸發部分水或加鹽</t>
+          <t>1%=10000ppm</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>水中某污染物2mg/1kg水約幾ppm？</t>
+          <t>水中某污染物2mg/1kg溶液約幾ppm？</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>3.5 g</t>
+          <t>2 ppm</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>37.5 g</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2 ppm</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">

--- a/02_加值成品/八上/八上2-4_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上2-4_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>如鹽</t>
+          <t>如鹽：溶液中被溶解、量通常較少的物質稱為溶質，例如鹽水中的鹽</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>常為水</t>
+          <t>常為水：溶液中負責溶解其他物質、量通常較多的物質稱為溶劑，日常生活中最常見的溶劑是水</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>兩者</t>
+          <t>兩者：溶液是溶質均勻分散溶解在溶劑中所形成的均勻混合物，由溶質和溶劑兩部分組成</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>含溶質</t>
+          <t>含溶質：重量百分濃度的定義是溶質質量除以溶液(溶質+溶劑)總質量再乘以100%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>極稀</t>
+          <t>極稀：ppm是百萬分之一的意思，用來表示極稀薄溶液中溶質所占的比例</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>溶劑是水</t>
+          <t>溶劑是水：食鹽水中被溶解的鹽是溶質，負責溶解鹽的水則是溶劑</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>總和</t>
+          <t>總和：溶液的總質量等於溶質質量加上溶劑質量的總和</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>醫療用</t>
+          <t>醫療用：生理食鹽水的濃度大約是0.9%，這個濃度和人體體液的濃度相近，常用於醫療注射或沖洗傷口</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>溶液</t>
+          <t>溶液：溶質均勻分散溶解在溶劑中所形成的均勻混合物稱為溶液</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>濃度</t>
+          <t>濃度：濃度是用來表示溶液中所含溶質相對多少的量，濃度越高代表溶質比例越多</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>20/100</t>
+          <t>20/100：濃度=溶質÷溶液，溶質20g加溶劑80g等於溶液100g，20÷100=20%</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>10/100</t>
+          <t>10/100：濃度=溶質÷溶液，溶質10g加溶劑90g等於溶液100g，10÷100=10%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>5/100</t>
+          <t>5/100：濃度=溶質÷溶液，5g除以100g等於5%</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>200×0.1</t>
+          <t>200×0.1：溶質質量=溶液質量×濃度，200克乘以10%等於20克</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>0.05/50×10⁶</t>
+          <t>0.05/50×10⁶：ppm是溶質除以溶液再乘以10⁶，0.05除以50再乘以100萬約等於1000ppm</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>只濃度降</t>
+          <t>只濃度降：加水稀釋只是增加溶劑量，原本溶質的質量並沒有減少或消失，只是分母(溶液總量)變大使濃度下降</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>30/150</t>
+          <t>30/150：濃度=溶質÷溶液，溶質30g加溶劑120g等於溶液150g，30÷150=20%</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>150×0.25</t>
+          <t>150×0.25：溶質質量=溶液質量×濃度，150克乘以25%等於37.5克</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>40/200</t>
+          <t>40/200：濃度=溶質÷溶液，溶質40g加溶劑160g等於溶液200g，40÷200=20%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>100×0.05</t>
+          <t>100×0.05：溶質質量=溶液質量×濃度，100公克乘以5%等於5公克</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>定義</t>
+          <t>定義：濃度要表示的是溶質在「整杯溶液」裡所佔的比例，溶液(溶質+溶劑)才是完整的總量，若只用溶劑當分母會少算溶質本身的量，比例就不準確</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>分母變大</t>
+          <t>分母變大：溶質質量不變，但加水後溶液總質量(分母)變大，濃度=溶質÷溶液，分母變大結果就變小</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>mg/kg</t>
+          <t>mg/kg：1公斤等於100萬毫克，2毫克除以100萬毫克再乘以100萬等於2ppm，剛好就是mg除以kg的數值</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>溶質不變總量少</t>
+          <t>溶質不變總量少：蒸發只讓水(溶劑)減少，溶質質量不變，溶液總量(分母)變小了，濃度=溶質÷溶液，分母變小結果就變大</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>同濃度</t>
+          <t>同濃度：兩杯溶液原本濃度相同，代表溶質和溶劑的比例相同，混合後這個比例不會改變，所以濃度仍然不變</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>稀釋</t>
+          <t>稀釋：加入純水等於增加溶劑，讓溶液總量變大而溶質不變，濃度會因此下降變小</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>提高溶質比</t>
+          <t>提高溶質比：要提高濃度可以蒸發掉部分水(讓溶劑減少)，或是直接加入更多鹽(讓溶質增加)，兩種方法都能提高溶質佔溶液的比例</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>換算</t>
+          <t>換算：%是百分之一(百分之一=萬分之一百)，ppm是百萬分之一，1%換算成ppm是10000ppm，也就是ppm比%的單位小上一萬倍</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>稀釋一半</t>
+          <t>稀釋一半：原本溶質質量=100×10%=10g，加水後溶質量不變，但溶液總量變成200g，10÷200=5%，濃度剛好減半</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>百分濃度</t>
+          <t>百分濃度：百分濃度是每100克溶液中含有多少克溶質，3.5%就代表每100克海水裡含有3.5克鹽</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八上/八上2-4_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上2-4_三種難度測驗卷.xlsx
@@ -563,7 +563,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>不變</t>
+          <t>變小</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -573,12 +573,12 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>溶劑</t>
+          <t>百萬分之一</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>鹽</t>
+          <t>變大</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -603,12 +603,12 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>溶液</t>
+          <t>多寡</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>變大</t>
+          <t>溶質</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>多寡</t>
+          <t>鹽</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -648,17 +648,17 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>鹽</t>
+          <t>變小</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>溶劑</t>
+          <t>不變</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>溶液</t>
+          <t>多寡</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -803,17 +803,17 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>變大</t>
+          <t>百萬分之一</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>百萬分之一</t>
+          <t>變小</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>溶劑</t>
+          <t>溶液</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1319,17 +1319,17 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
           <t>3.5 g</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>5 g</t>
-        </is>
-      </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>20 g</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>37.5 g</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -1409,12 +1409,12 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>20 g</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>3.5 g</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1875,17 +1875,17 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
           <t>37.5 g</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>20 g</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>5 g</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
